--- a/Inventario.xlsx
+++ b/Inventario.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>FechaIngreso</t>
   </si>
@@ -30,21 +30,6 @@
   </si>
   <si>
     <t>ValorTotal</t>
-  </si>
-  <si>
-    <t>2024-10-31  Hora:  12:29</t>
-  </si>
-  <si>
-    <t>hols</t>
-  </si>
-  <si>
-    <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>9.0</t>
   </si>
 </sst>
 </file>
@@ -89,7 +74,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -112,26 +97,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Inventario.xlsx
+++ b/Inventario.xlsx
@@ -12,15 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>FechaIngreso</t>
   </si>
   <si>
-    <t>Nombre</t>
+    <t>Bodegas</t>
   </si>
   <si>
-    <t>FechaCompra</t>
+    <t>Nombre</t>
   </si>
   <si>
     <t>Cantidad</t>
@@ -30,6 +30,42 @@
   </si>
   <si>
     <t>ValorTotal</t>
+  </si>
+  <si>
+    <t>2024-10-31  Hora:  20:40</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>cemento</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2024-10-31  Hora:  20:43</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>tornilloss</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>5500</t>
+  </si>
+  <si>
+    <t>242000</t>
   </si>
 </sst>
 </file>
@@ -74,7 +110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -97,6 +133,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Inventario.xlsx
+++ b/Inventario.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>FechaIngreso</t>
   </si>
@@ -50,22 +50,64 @@
     <t>100000</t>
   </si>
   <si>
-    <t>2024-10-31  Hora:  20:43</t>
+    <t>2024-11-01  Hora:  11:32</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>metal</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>tornilloss</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>5500</t>
-  </si>
-  <si>
-    <t>242000</t>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>2024-11-01  Hora:  11:37</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>600000</t>
+  </si>
+  <si>
+    <t>2024-11-01  Hora:  12:11</t>
+  </si>
+  <si>
+    <t>palermo</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>250000</t>
+  </si>
+  <si>
+    <t>2024-11-01  Hora:  12:14</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>2024-11-01  Hora:  12:29</t>
+  </si>
+  <si>
+    <t>brisas</t>
+  </si>
+  <si>
+    <t>barrillas</t>
   </si>
 </sst>
 </file>
@@ -110,7 +152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -173,6 +215,86 @@
         <v>17</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Inventario.xlsx
+++ b/Inventario.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
   <si>
     <t>FechaIngreso</t>
   </si>
@@ -32,82 +32,118 @@
     <t>ValorTotal</t>
   </si>
   <si>
-    <t>2024-10-31  Hora:  20:40</t>
+    <t>2024-11-01  Hora:  11:32</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>metal</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>2024-11-01  Hora:  11:37</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>600000</t>
+  </si>
+  <si>
+    <t>2024-11-01  Hora:  12:11</t>
+  </si>
+  <si>
+    <t>palermo</t>
+  </si>
+  <si>
+    <t>cemento</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>250000</t>
+  </si>
+  <si>
+    <t>2024-11-01  Hora:  12:14</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2024-11-01  Hora:  12:29</t>
+  </si>
+  <si>
+    <t>brisas</t>
+  </si>
+  <si>
+    <t>barrillas</t>
+  </si>
+  <si>
+    <t>2024-11-05  Hora:  15:56</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>cemento</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>1320000</t>
+  </si>
+  <si>
+    <t>2024-11-05  Hora:  15:57</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>110000</t>
+  </si>
+  <si>
+    <t>2024-11-05  Hora:  16:02</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>10000</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2024-11-01  Hora:  11:32</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>metal</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>70000</t>
-  </si>
-  <si>
-    <t>2024-11-01  Hora:  11:37</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>600000</t>
-  </si>
-  <si>
-    <t>2024-11-01  Hora:  12:11</t>
-  </si>
-  <si>
-    <t>palermo</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>250000</t>
-  </si>
-  <si>
-    <t>2024-11-01  Hora:  12:14</t>
-  </si>
-  <si>
-    <t>20000</t>
-  </si>
-  <si>
-    <t>2024-11-01  Hora:  12:29</t>
-  </si>
-  <si>
-    <t>brisas</t>
-  </si>
-  <si>
-    <t>barrillas</t>
   </si>
 </sst>
 </file>
@@ -152,7 +188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -203,96 +239,156 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
         <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Inventario.xlsx
+++ b/Inventario.xlsx
@@ -101,43 +101,43 @@
     <t>2024-11-05  Hora:  15:56</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>1320000</t>
+  </si>
+  <si>
+    <t>2024-11-05  Hora:  15:57</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>110000</t>
+  </si>
+  <si>
+    <t>2024-11-05  Hora:  16:02</t>
+  </si>
+  <si>
     <t>23</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>1320000</t>
-  </si>
-  <si>
-    <t>2024-11-05  Hora:  15:57</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>110000</t>
-  </si>
-  <si>
-    <t>2024-11-05  Hora:  16:02</t>
   </si>
   <si>
     <t>25</t>
@@ -336,19 +336,19 @@
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -356,27 +356,27 @@
         <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
         <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>

--- a/Inventario.xlsx
+++ b/Inventario.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>FechaIngreso</t>
   </si>
@@ -144,6 +144,15 @@
   </si>
   <si>
     <t>10000</t>
+  </si>
+  <si>
+    <t>2024-11-13  Hora:  09:32</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>5000</t>
   </si>
 </sst>
 </file>
@@ -188,7 +197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -391,6 +400,26 @@
         <v>21</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
